--- a/dados/prestadores.xlsx
+++ b/dados/prestadores.xlsx
@@ -9719,7 +9719,7 @@
     <t>08137265247</t>
   </si>
   <si>
-    <t>8137265247</t>
+    <t>558137265247</t>
   </si>
   <si>
     <t>28440273000176</t>
